--- a/3D Printing Files/Print Qtys.xlsx
+++ b/3D Printing Files/Print Qtys.xlsx
@@ -1157,8 +1157,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="09e37f2ef9bef24154c689c9241203a8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c23ee64ebe9444b24c4b4ef6420ff96" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
     <xsd:import namespace="fb0bfce0-b493-4733-b695-336371de64d4"/>
     <xsd:element name="properties">
@@ -1389,20 +1389,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2E3AC0-1A4A-4B9F-87CA-78D702EC95D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
-    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20BC13A3-AB28-4635-B939-5CC4A5B57516}"/>
 </file>
--- a/3D Printing Files/Print Qtys.xlsx
+++ b/3D Printing Files/Print Qtys.xlsx
@@ -1157,8 +1157,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="09e37f2ef9bef24154c689c9241203a8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c23ee64ebe9444b24c4b4ef6420ff96" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
     <xsd:import namespace="fb0bfce0-b493-4733-b695-336371de64d4"/>
     <xsd:element name="properties">
@@ -1389,20 +1389,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2E3AC0-1A4A-4B9F-87CA-78D702EC95D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
-    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD1EEC8-9179-4CEC-B0B0-EFE4AC05A460}"/>
 </file>